--- a/artfynd/A 41379-2022 artfynd.xlsx
+++ b/artfynd/A 41379-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41379-2022 artfynd.xlsx
+++ b/artfynd/A 41379-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104172429</v>
+        <v>104172440</v>
       </c>
       <c r="B2" t="n">
-        <v>79433</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1049</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>350932.49742813</v>
+        <v>351011</v>
       </c>
       <c r="R2" t="n">
-        <v>6587025.460380007</v>
+        <v>6586949</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,28 +747,17 @@
           <t>2022-05-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-05-19</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -791,56 +776,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104172439</v>
+        <v>104216925</v>
       </c>
       <c r="B3" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hynningen, Vrm</t>
+          <t>Årjäng, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>351010.192944269</v>
+        <v>351045</v>
       </c>
       <c r="R3" t="n">
-        <v>6586949.49031848</v>
+        <v>6586961</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,22 +842,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-05-19</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-05-19</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,65 +872,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jeanette Fahlstad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jeanette Fahlstad, Roger Gran</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104172438</v>
+        <v>105127744</v>
       </c>
       <c r="B4" t="n">
-        <v>89794</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5321</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hynningen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>351010.192944269</v>
+        <v>350967</v>
       </c>
       <c r="R4" t="n">
-        <v>6586949.49031848</v>
+        <v>6586938</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,22 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-05-19</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-05-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,27 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jeanette Fahlstad</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jeanette Fahlstad, Roger Gran</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104172431</v>
+        <v>105127749</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,42 +992,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hynningen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>351004.0901180717</v>
+        <v>350917</v>
       </c>
       <c r="R5" t="n">
-        <v>6586988.987577141</v>
+        <v>6586935</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,22 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-05-19</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-05-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,27 +1066,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jeanette Fahlstad</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jeanette Fahlstad, Roger Gran</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104172427</v>
+        <v>105127755</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,37 +1089,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hynningen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>350909.4038216217</v>
+        <v>350887</v>
       </c>
       <c r="R6" t="n">
-        <v>6586932.054175001</v>
+        <v>6586879</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,22 +1143,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-05-19</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-05-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,34 +1157,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jeanette Fahlstad</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jeanette Fahlstad, Roger Gran</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104172440</v>
+        <v>104172429</v>
       </c>
       <c r="B7" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,27 +1186,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1301,10 +1213,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>351010.192944269</v>
+        <v>350932</v>
       </c>
       <c r="R7" t="n">
-        <v>6586949.49031848</v>
+        <v>6587025</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,27 +1246,18 @@
           <t>2022-05-19</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-05-19</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1373,15 +1276,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104216925</v>
+        <v>104172427</v>
       </c>
       <c r="B8" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,38 +1287,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Årjäng, Vrm</t>
+          <t>Hynningen, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>351045.3696814069</v>
+        <v>350910</v>
       </c>
       <c r="R8" t="n">
-        <v>6586960.848694188</v>
+        <v>6586933</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,22 +1344,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:44</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:44</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,33 +1358,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Jeanette Fahlstad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Jeanette Fahlstad, Roger Gran</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105127755</v>
+        <v>105127746</v>
       </c>
       <c r="B9" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,21 +1388,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1526,10 +1412,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>350887.3866849376</v>
+        <v>350960</v>
       </c>
       <c r="R9" t="n">
-        <v>6586878.880700015</v>
+        <v>6586933</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,19 +1445,9 @@
           <t>2022-11-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-11-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,15 +1474,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105127751</v>
+        <v>104172438</v>
       </c>
       <c r="B10" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,34 +1485,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>5321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hynningen, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>350908.9015418292</v>
+        <v>351011</v>
       </c>
       <c r="R10" t="n">
-        <v>6586919.32819259</v>
+        <v>6586949</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,22 +1542,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-11-29</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-11-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,49 +1562,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Jeanette Fahlstad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Jeanette Fahlstad, Roger Gran</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105127749</v>
+        <v>105127751</v>
       </c>
       <c r="B11" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1750,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>350917.7032953297</v>
+        <v>350909</v>
       </c>
       <c r="R11" t="n">
-        <v>6586935.295431148</v>
+        <v>6586919</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,19 +1642,9 @@
           <t>2022-11-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-11-29</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,16 +1674,11 @@
         <v>105127743</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1862,10 +1706,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>350973.7551370745</v>
+        <v>350974</v>
       </c>
       <c r="R12" t="n">
-        <v>6586932.064004591</v>
+        <v>6586932</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,19 +1739,9 @@
           <t>2022-11-29</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-11-29</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,15 +1768,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>105127746</v>
+        <v>105127747</v>
       </c>
       <c r="B13" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1950,21 +1779,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1974,10 +1803,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>350959.4771658452</v>
+        <v>350939</v>
       </c>
       <c r="R13" t="n">
-        <v>6586932.627323803</v>
+        <v>6586930</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,19 +1836,9 @@
           <t>2022-11-29</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-11-29</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2046,15 +1865,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105127744</v>
+        <v>110077548</v>
       </c>
       <c r="B14" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2062,21 +1876,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2086,10 +1900,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>350966.3271424449</v>
+        <v>350818</v>
       </c>
       <c r="R14" t="n">
-        <v>6586937.965193129</v>
+        <v>6586861</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2116,22 +1930,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-11-29</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-11-29</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,27 +1950,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Jan Rees, Roger Gran</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>105127747</v>
+        <v>104172439</v>
       </c>
       <c r="B15" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2174,34 +1973,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hynningen, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>350938.4094410569</v>
+        <v>351011</v>
       </c>
       <c r="R15" t="n">
-        <v>6586929.379973727</v>
+        <v>6586949</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2228,22 +2030,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-11-29</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-11-29</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,44 +2050,39 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Jeanette Fahlstad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Jeanette Fahlstad, Roger Gran</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>110077551</v>
+        <v>104172431</v>
       </c>
       <c r="B16" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2304,12 +2091,11 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2319,10 +2105,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>350915.1584199088</v>
+        <v>351004</v>
       </c>
       <c r="R16" t="n">
-        <v>6586961.397156841</v>
+        <v>6586990</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2349,22 +2135,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-05-29</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-05-29</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2373,69 +2149,68 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Jeanette Fahlstad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jan Rees, Roger Gran</t>
+          <t>Jeanette Fahlstad, Roger Gran</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>110077547</v>
+        <v>108701216</v>
       </c>
       <c r="B17" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hynningen, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>350818.7612287594</v>
+        <v>351067</v>
       </c>
       <c r="R17" t="n">
-        <v>6586861.196614759</v>
+        <v>6586946</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2462,22 +2237,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-05-29</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-05-29</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,57 +2262,61 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jan Rees, Roger Gran</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>110077548</v>
+        <v>110077551</v>
       </c>
       <c r="B18" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>105930</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hynningen, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>350818.7612287594</v>
+        <v>350915</v>
       </c>
       <c r="R18" t="n">
-        <v>6586861.196614759</v>
+        <v>6586961</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2577,27 +2346,18 @@
           <t>2023-05-29</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-05-29</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2613,6 +2373,103 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>110077547</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hynningen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>350818</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6586861</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jan Rees, Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
